--- a/etf_holdings/2026-09-07_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-07_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -496,60 +496,60 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>7.94%</t>
+          <t>4.91%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8.57%</t>
+          <t>4.86%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5088000</v>
+        <v>183000</v>
       </c>
       <c r="K2" t="n">
-        <v>5186000</v>
+        <v>182000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>98,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-06_00981A_full_holdings.xlsx</t>
+          <t>2026-09-06_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,55 +564,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4591848</v>
+        <v>3258000</v>
       </c>
       <c r="K3" t="n">
-        <v>4403848</v>
+        <v>3251000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-188,000</t>
+          <t>-7,000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-06_00981A_full_holdings.xlsx</t>
+          <t>2026-09-06_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -622,32 +622,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -656,26 +656,26 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2157000</v>
+        <v>5205000</v>
       </c>
       <c r="K4" t="n">
-        <v>2712000</v>
+        <v>5190000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>555,000</t>
+          <t>-15,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-06_00981A_full_holdings.xlsx</t>
+          <t>2026-09-06_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -690,55 +690,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2184000</v>
+        <v>830000</v>
       </c>
       <c r="K5" t="n">
-        <v>924000</v>
+        <v>827000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-1,260,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-06_00981A_full_holdings.xlsx</t>
+          <t>2026-09-06_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -748,60 +748,60 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>561000</v>
+        <v>1773000</v>
       </c>
       <c r="K6" t="n">
-        <v>637000</v>
+        <v>1767000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>76,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-06_00981A_full_holdings.xlsx</t>
+          <t>2026-09-06_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -816,55 +816,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2427000</v>
+        <v>4322000</v>
       </c>
       <c r="K7" t="n">
-        <v>2184000</v>
+        <v>4308000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-243,000</t>
+          <t>-14,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-06_00981A_full_holdings.xlsx</t>
+          <t>2026-09-06_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -879,48 +879,48 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>3.31%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1300000</v>
+        <v>315000</v>
       </c>
       <c r="K8" t="n">
-        <v>1040000</v>
+        <v>314000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-260,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-09-06_00981A_full_holdings.xlsx</t>
+          <t>2026-09-06_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -942,43 +942,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.86%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>183000</v>
+        <v>1466000</v>
       </c>
       <c r="K9" t="n">
-        <v>182000</v>
+        <v>1463000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1005,43 +1005,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>興勤</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>興勤</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3258000</v>
+        <v>2318000</v>
       </c>
       <c r="K10" t="n">
-        <v>3251000</v>
+        <v>2310000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-7,000</t>
+          <t>-8,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1068,43 +1068,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>5205000</v>
+        <v>1553000</v>
       </c>
       <c r="K11" t="n">
-        <v>5190000</v>
+        <v>1549000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-15,000</t>
+          <t>-4,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1131,43 +1131,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>830000</v>
+        <v>1285000</v>
       </c>
       <c r="K12" t="n">
-        <v>827000</v>
+        <v>1281000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>-4,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1194,27 +1194,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>大毅</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>大毅</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1223,14 +1223,14 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1773000</v>
+        <v>4418000</v>
       </c>
       <c r="K13" t="n">
-        <v>1767000</v>
+        <v>4404000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>-14,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1257,43 +1257,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>2.45%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>4322000</v>
+        <v>374000</v>
       </c>
       <c r="K14" t="n">
-        <v>4308000</v>
+        <v>373000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-14,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1320,43 +1320,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>315000</v>
+        <v>3346000</v>
       </c>
       <c r="K15" t="n">
-        <v>314000</v>
+        <v>3335000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-11,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1383,43 +1383,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1466000</v>
+        <v>3704000</v>
       </c>
       <c r="K16" t="n">
-        <v>1463000</v>
+        <v>3693000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>-11,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1446,17 +1446,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>興勤</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>興勤</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1475,14 +1475,14 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>2318000</v>
+        <v>3418000</v>
       </c>
       <c r="K17" t="n">
-        <v>2310000</v>
+        <v>3406000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-8,000</t>
+          <t>-12,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1509,43 +1509,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1553000</v>
+        <v>1145000</v>
       </c>
       <c r="K18" t="n">
-        <v>1549000</v>
+        <v>1110000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-4,000</t>
+          <t>-35,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1572,27 +1572,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>碩天</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>碩天</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1601,14 +1601,14 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1285000</v>
+        <v>579000</v>
       </c>
       <c r="K19" t="n">
-        <v>1281000</v>
+        <v>577000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-4,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1635,17 +1635,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>大毅</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>大毅</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1655,23 +1655,23 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>4418000</v>
+        <v>942000</v>
       </c>
       <c r="K20" t="n">
-        <v>4404000</v>
+        <v>939000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-14,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1698,43 +1698,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>374000</v>
+        <v>6445000</v>
       </c>
       <c r="K21" t="n">
-        <v>373000</v>
+        <v>6435000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-10,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1761,39 +1761,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>日電貿</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>日電貿</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3346000</v>
+        <v>3481000</v>
       </c>
       <c r="K22" t="n">
-        <v>3335000</v>
+        <v>3470000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1824,43 +1824,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>5.37%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>5.33%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3704000</v>
+        <v>3771000</v>
       </c>
       <c r="K23" t="n">
-        <v>3693000</v>
+        <v>3758000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-11,000</t>
+          <t>-13,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1887,43 +1887,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>3418000</v>
+        <v>305000</v>
       </c>
       <c r="K24" t="n">
-        <v>3406000</v>
+        <v>304000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-12,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1950,43 +1950,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1145000</v>
+        <v>428000</v>
       </c>
       <c r="K25" t="n">
-        <v>1110000</v>
+        <v>426000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-35,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2008,22 +2008,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>碩天</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>碩天</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2033,23 +2033,23 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>579000</v>
+        <v>115000</v>
       </c>
       <c r="K26" t="n">
-        <v>577000</v>
+        <v>116000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2076,43 +2076,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>942000</v>
+        <v>537000</v>
       </c>
       <c r="K27" t="n">
-        <v>939000</v>
+        <v>535000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2139,43 +2139,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>6445000</v>
+        <v>2807000</v>
       </c>
       <c r="K28" t="n">
-        <v>6435000</v>
+        <v>2792000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-10,000</t>
+          <t>-15,000</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2187,7 +2187,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2197,60 +2197,60 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>4.05%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>3481000</v>
+        <v>50000000</v>
       </c>
       <c r="K29" t="n">
-        <v>3470000</v>
+        <v>55000000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-11,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-06_00982A_full_holdings.xlsx</t>
+          <t>2026-09-06_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2265,55 +2265,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5.37%</t>
+          <t>15.47%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5.33%</t>
+          <t>15.47%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>3771000</v>
+        <v>10300000</v>
       </c>
       <c r="K30" t="n">
-        <v>3758000</v>
+        <v>10100000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-13,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-06_00982A_full_holdings.xlsx</t>
+          <t>2026-09-06_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2323,60 +2323,60 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>305000</v>
+        <v>1700000</v>
       </c>
       <c r="K31" t="n">
-        <v>304000</v>
+        <v>2600000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09-06_00982A_full_holdings.xlsx</t>
+          <t>2026-09-06_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2386,60 +2386,60 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>5.80%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>6.55%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.75%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>428000</v>
+        <v>2110000</v>
       </c>
       <c r="K32" t="n">
-        <v>426000</v>
+        <v>2210000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09-06_00982A_full_holdings.xlsx</t>
+          <t>2026-09-06_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2454,55 +2454,55 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>115000</v>
+        <v>2000000</v>
       </c>
       <c r="K33" t="n">
-        <v>116000</v>
+        <v>3000000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-06_00982A_full_holdings.xlsx</t>
+          <t>2026-09-06_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2517,55 +2517,55 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>3.39%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>537000</v>
+        <v>736000</v>
       </c>
       <c r="K34" t="n">
-        <v>535000</v>
+        <v>686000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-50,000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09-06_00982A_full_holdings.xlsx</t>
+          <t>2026-09-06_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2580,48 +2580,48 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>2.35%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>2807000</v>
+        <v>650000</v>
       </c>
       <c r="K35" t="n">
-        <v>2792000</v>
+        <v>580000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-15,000</t>
+          <t>-70,000</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-09-06_00982A_full_holdings.xlsx</t>
+          <t>2026-09-06_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -2638,48 +2638,48 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>50000000</v>
+        <v>4500000</v>
       </c>
       <c r="K36" t="n">
-        <v>55000000</v>
+        <v>4000000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>-500,000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2706,43 +2706,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>15.47%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>15.47%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>10300000</v>
+        <v>1737000</v>
       </c>
       <c r="K37" t="n">
-        <v>10100000</v>
+        <v>1580000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-200,000</t>
+          <t>-157,000</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2754,133 +2754,97 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>0.28%</t>
-        </is>
-      </c>
+          <t>微星科技</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.44%</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>+0.16%</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>1700000</v>
-      </c>
+          <t>1.86%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
-        <v>2600000</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>900,000</t>
-        </is>
-      </c>
+        <v>1213000</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-06_00403A_full_holdings.xlsx</t>
+          <t>2026-09-06_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
+          <t>臻鼎科技控股</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>5.80%</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>6.55%</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>+0.75%</t>
-        </is>
-      </c>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>2110000</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2210000</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>100,000</t>
-        </is>
-      </c>
+        <v>46000</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-06_00403A_full_holdings.xlsx</t>
+          <t>2026-09-06_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2890,60 +2854,60 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>大成不銹鋼工業</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>大成不銹鋼工業</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>2000000</v>
+        <v>4181000</v>
       </c>
       <c r="K40" t="n">
-        <v>3000000</v>
+        <v>2097000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>-2,084,000</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-09-06_00403A_full_holdings.xlsx</t>
+          <t>2026-09-06_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2953,60 +2917,60 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>鴻海精密工業</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>鴻海精密工業</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.48%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>+0.98%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>736000</v>
+        <v>629000</v>
       </c>
       <c r="K41" t="n">
-        <v>686000</v>
+        <v>1021000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-50,000</t>
+          <t>392,000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-09-06_00403A_full_holdings.xlsx</t>
+          <t>2026-09-06_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3021,55 +2985,55 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>金像電子（股）公司</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>金像電子（股）公司</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>650000</v>
+        <v>19000</v>
       </c>
       <c r="K42" t="n">
-        <v>580000</v>
+        <v>1000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-70,000</t>
+          <t>-18,000</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-09-06_00403A_full_holdings.xlsx</t>
+          <t>2026-09-06_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3079,60 +3043,60 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>4500000</v>
+        <v>313000</v>
       </c>
       <c r="K43" t="n">
-        <v>4000000</v>
+        <v>444000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-500,000</t>
+          <t>131,000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-09-06_00403A_full_holdings.xlsx</t>
+          <t>2026-09-06_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3147,48 +3111,48 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>文曄科技</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>文曄科技</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>1737000</v>
+        <v>27000</v>
       </c>
       <c r="K44" t="n">
-        <v>1580000</v>
+        <v>1000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-157,000</t>
+          <t>-26,000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-06_00403A_full_holdings.xlsx</t>
+          <t>2026-09-06_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -3200,37 +3164,55 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2377</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>穩懋半導體</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>微星科技</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>穩懋半導體</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.86%</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>-0.86%</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>203000</v>
+      </c>
       <c r="K45" t="n">
-        <v>1213000</v>
-      </c>
-      <c r="L45" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>-201,000</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>2026-09-06_00985A_full_holdings.xlsx</t>
@@ -3245,37 +3227,55 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>臻鼎科技控股</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.21%</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
       <c r="J46" t="n">
-        <v>46000</v>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>2026-09-06_00985A_full_holdings.xlsx</t>
@@ -3300,43 +3300,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>大成不銹鋼工業</t>
+          <t>緯穎科技服務</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>大成不銹鋼工業</t>
+          <t>緯穎科技服務</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>3.99%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>4181000</v>
+        <v>167036</v>
       </c>
       <c r="K47" t="n">
-        <v>2097000</v>
+        <v>114036</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-2,084,000</t>
+          <t>-53,000</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3358,48 +3358,48 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>鴻海精密工業</t>
+          <t>群聯電子</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>鴻海精密工業</t>
+          <t>群聯電子</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>629000</v>
+        <v>9000</v>
       </c>
       <c r="K48" t="n">
-        <v>1021000</v>
+        <v>1000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>392,000</t>
+          <t>-8,000</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3411,7 +3411,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3421,60 +3421,60 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>金像電子（股）公司</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>金像電子（股）公司</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>2.29%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>19000</v>
+        <v>123000</v>
       </c>
       <c r="K49" t="n">
-        <v>1000</v>
+        <v>175000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-18,000</t>
+          <t>52,000</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-06_00985A_full_holdings.xlsx</t>
+          <t>2026-09-06_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3484,60 +3484,60 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>3.92%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>-1.15%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>313000</v>
+        <v>154000</v>
       </c>
       <c r="K50" t="n">
-        <v>444000</v>
+        <v>121000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>131,000</t>
+          <t>-33,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-06_00985A_full_holdings.xlsx</t>
+          <t>2026-09-06_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3547,60 +3547,60 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>4.13%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4.42%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>27000</v>
+        <v>336000</v>
       </c>
       <c r="K51" t="n">
-        <v>1000</v>
+        <v>377000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-26,000</t>
+          <t>41,000</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-09-06_00985A_full_holdings.xlsx</t>
+          <t>2026-09-06_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3610,492 +3610,51 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>穩懋半導體</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>穩懋半導體</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>2.81%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>3.94%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>203000</v>
+        <v>907000</v>
       </c>
       <c r="K52" t="n">
-        <v>2000</v>
+        <v>1209000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-201,000</t>
+          <t>302,000</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
-        <is>
-          <t>2026-09-06_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>景碩科技</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>景碩科技</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>-1,000</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>2026-09-06_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>緯穎科技服務</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>緯穎科技服務</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>3.99%</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>2.78%</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>-1.21%</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>167036</v>
-      </c>
-      <c r="K54" t="n">
-        <v>114036</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>-53,000</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>2026-09-06_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>群聯電子</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>群聯電子</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>0.02%</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>-0.15%</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>9000</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>-8,000</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>2026-09-06_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2.29%</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>3.30%</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>+1.01%</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>123000</v>
-      </c>
-      <c r="K56" t="n">
-        <v>175000</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>52,000</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>2026-09-06_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>3.92%</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>2.77%</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>-1.15%</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>154000</v>
-      </c>
-      <c r="K57" t="n">
-        <v>121000</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>-33,000</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>2026-09-06_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>4.13%</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>4.42%</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>+0.29%</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>336000</v>
-      </c>
-      <c r="K58" t="n">
-        <v>377000</v>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>41,000</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>2026-09-06_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2.81%</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>3.94%</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>+1.13%</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>907000</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1209000</v>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>302,000</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
         <is>
           <t>2026-09-06_00400A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-09-07_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-07_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -496,60 +496,60 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>7.94%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4.86%</t>
+          <t>8.57%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>183000</v>
+        <v>5088000</v>
       </c>
       <c r="K2" t="n">
-        <v>182000</v>
+        <v>5186000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>98,000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-06_00982A_full_holdings.xlsx</t>
+          <t>2026-09-06_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,55 +564,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>3.48%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>3.16%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3258000</v>
+        <v>4591848</v>
       </c>
       <c r="K3" t="n">
-        <v>3251000</v>
+        <v>4403848</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-7,000</t>
+          <t>-188,000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-06_00982A_full_holdings.xlsx</t>
+          <t>2026-09-06_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -622,32 +622,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -656,26 +656,26 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5205000</v>
+        <v>2157000</v>
       </c>
       <c r="K4" t="n">
-        <v>5190000</v>
+        <v>2712000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-15,000</t>
+          <t>555,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-06_00982A_full_holdings.xlsx</t>
+          <t>2026-09-06_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -690,55 +690,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>830000</v>
+        <v>2184000</v>
       </c>
       <c r="K5" t="n">
-        <v>827000</v>
+        <v>924000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>-1,260,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-06_00982A_full_holdings.xlsx</t>
+          <t>2026-09-06_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -748,60 +748,60 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1773000</v>
+        <v>561000</v>
       </c>
       <c r="K6" t="n">
-        <v>1767000</v>
+        <v>637000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-6,000</t>
+          <t>76,000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-06_00982A_full_holdings.xlsx</t>
+          <t>2026-09-06_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -816,55 +816,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>4322000</v>
+        <v>2427000</v>
       </c>
       <c r="K7" t="n">
-        <v>4308000</v>
+        <v>2184000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-14,000</t>
+          <t>-243,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-06_00982A_full_holdings.xlsx</t>
+          <t>2026-09-06_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -879,48 +879,48 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>315000</v>
+        <v>1300000</v>
       </c>
       <c r="K8" t="n">
-        <v>314000</v>
+        <v>1040000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-260,000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-09-06_00982A_full_holdings.xlsx</t>
+          <t>2026-09-06_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -942,43 +942,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>4.91%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>4.86%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1466000</v>
+        <v>183000</v>
       </c>
       <c r="K9" t="n">
-        <v>1463000</v>
+        <v>182000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1005,43 +1005,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>興勤</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>興勤</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2318000</v>
+        <v>3258000</v>
       </c>
       <c r="K10" t="n">
-        <v>2310000</v>
+        <v>3251000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-8,000</t>
+          <t>-7,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1068,43 +1068,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1553000</v>
+        <v>5205000</v>
       </c>
       <c r="K11" t="n">
-        <v>1549000</v>
+        <v>5190000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-4,000</t>
+          <t>-15,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1131,43 +1131,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1285000</v>
+        <v>830000</v>
       </c>
       <c r="K12" t="n">
-        <v>1281000</v>
+        <v>827000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-4,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1194,27 +1194,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>大毅</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>大毅</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1223,14 +1223,14 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>4418000</v>
+        <v>1773000</v>
       </c>
       <c r="K13" t="n">
-        <v>4404000</v>
+        <v>1767000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-14,000</t>
+          <t>-6,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1257,43 +1257,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>374000</v>
+        <v>4322000</v>
       </c>
       <c r="K14" t="n">
-        <v>373000</v>
+        <v>4308000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-14,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1320,43 +1320,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>日電貿</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>日電貿</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>3.31%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3346000</v>
+        <v>315000</v>
       </c>
       <c r="K15" t="n">
-        <v>3335000</v>
+        <v>314000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-11,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1383,43 +1383,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3704000</v>
+        <v>1466000</v>
       </c>
       <c r="K16" t="n">
-        <v>3693000</v>
+        <v>1463000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-11,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1446,17 +1446,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>興勤</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>興勤</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1475,14 +1475,14 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3418000</v>
+        <v>2318000</v>
       </c>
       <c r="K17" t="n">
-        <v>3406000</v>
+        <v>2310000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-12,000</t>
+          <t>-8,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1509,43 +1509,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1145000</v>
+        <v>1553000</v>
       </c>
       <c r="K18" t="n">
-        <v>1110000</v>
+        <v>1549000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-35,000</t>
+          <t>-4,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1572,27 +1572,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>碩天</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>碩天</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1601,14 +1601,14 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>579000</v>
+        <v>1285000</v>
       </c>
       <c r="K19" t="n">
-        <v>577000</v>
+        <v>1281000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-4,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1635,17 +1635,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>大毅</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>大毅</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1655,23 +1655,23 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>942000</v>
+        <v>4418000</v>
       </c>
       <c r="K20" t="n">
-        <v>939000</v>
+        <v>4404000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>-14,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1698,43 +1698,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>2.45%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>6445000</v>
+        <v>374000</v>
       </c>
       <c r="K21" t="n">
-        <v>6435000</v>
+        <v>373000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-10,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1761,39 +1761,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3481000</v>
+        <v>3346000</v>
       </c>
       <c r="K22" t="n">
-        <v>3470000</v>
+        <v>3335000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1824,43 +1824,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5.37%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5.33%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3771000</v>
+        <v>3704000</v>
       </c>
       <c r="K23" t="n">
-        <v>3758000</v>
+        <v>3693000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-13,000</t>
+          <t>-11,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1887,43 +1887,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>305000</v>
+        <v>3418000</v>
       </c>
       <c r="K24" t="n">
-        <v>304000</v>
+        <v>3406000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-12,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1950,43 +1950,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>428000</v>
+        <v>1145000</v>
       </c>
       <c r="K25" t="n">
-        <v>426000</v>
+        <v>1110000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-35,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2008,22 +2008,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>碩天</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>碩天</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2033,23 +2033,23 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>115000</v>
+        <v>579000</v>
       </c>
       <c r="K26" t="n">
-        <v>116000</v>
+        <v>577000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2076,43 +2076,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>537000</v>
+        <v>942000</v>
       </c>
       <c r="K27" t="n">
-        <v>535000</v>
+        <v>939000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2139,43 +2139,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>2807000</v>
+        <v>6445000</v>
       </c>
       <c r="K28" t="n">
-        <v>2792000</v>
+        <v>6435000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-15,000</t>
+          <t>-10,000</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2187,7 +2187,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2197,60 +2197,60 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>50000000</v>
+        <v>3481000</v>
       </c>
       <c r="K29" t="n">
-        <v>55000000</v>
+        <v>3470000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>-11,000</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-06_00403A_full_holdings.xlsx</t>
+          <t>2026-09-06_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2265,55 +2265,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>15.47%</t>
+          <t>5.37%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>15.47%</t>
+          <t>5.33%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>10300000</v>
+        <v>3771000</v>
       </c>
       <c r="K30" t="n">
-        <v>10100000</v>
+        <v>3758000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-200,000</t>
+          <t>-13,000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-06_00403A_full_holdings.xlsx</t>
+          <t>2026-09-06_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2323,60 +2323,60 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>1700000</v>
+        <v>305000</v>
       </c>
       <c r="K31" t="n">
-        <v>2600000</v>
+        <v>304000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09-06_00403A_full_holdings.xlsx</t>
+          <t>2026-09-06_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2386,60 +2386,60 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>5.80%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6.55%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>2110000</v>
+        <v>428000</v>
       </c>
       <c r="K32" t="n">
-        <v>2210000</v>
+        <v>426000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09-06_00403A_full_holdings.xlsx</t>
+          <t>2026-09-06_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2454,55 +2454,55 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>2000000</v>
+        <v>115000</v>
       </c>
       <c r="K33" t="n">
-        <v>3000000</v>
+        <v>116000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-06_00403A_full_holdings.xlsx</t>
+          <t>2026-09-06_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2517,55 +2517,55 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>736000</v>
+        <v>537000</v>
       </c>
       <c r="K34" t="n">
-        <v>686000</v>
+        <v>535000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-50,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09-06_00403A_full_holdings.xlsx</t>
+          <t>2026-09-06_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2580,48 +2580,48 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>650000</v>
+        <v>2807000</v>
       </c>
       <c r="K35" t="n">
-        <v>580000</v>
+        <v>2792000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-70,000</t>
+          <t>-15,000</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-09-06_00403A_full_holdings.xlsx</t>
+          <t>2026-09-06_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -2638,48 +2638,48 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>4.05%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>4500000</v>
+        <v>50000000</v>
       </c>
       <c r="K36" t="n">
-        <v>4000000</v>
+        <v>55000000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-500,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2706,43 +2706,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>15.47%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>15.47%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>1737000</v>
+        <v>10300000</v>
       </c>
       <c r="K37" t="n">
-        <v>1580000</v>
+        <v>10100000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-157,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2754,97 +2754,133 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2377</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>微星科技</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.86%</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>0.44%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>+0.16%</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1700000</v>
+      </c>
       <c r="K38" t="n">
-        <v>1213000</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
+        <v>2600000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>900,000</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-06_00985A_full_holdings.xlsx</t>
+          <t>2026-09-06_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>臻鼎科技控股</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.21%</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+          <t>5.80%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6.55%</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>+0.75%</t>
+        </is>
+      </c>
       <c r="J39" t="n">
-        <v>46000</v>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+        <v>2110000</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2210000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-06_00985A_full_holdings.xlsx</t>
+          <t>2026-09-06_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2854,60 +2890,60 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>大成不銹鋼工業</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>大成不銹鋼工業</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>4181000</v>
+        <v>2000000</v>
       </c>
       <c r="K40" t="n">
-        <v>2097000</v>
+        <v>3000000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-2,084,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-09-06_00985A_full_holdings.xlsx</t>
+          <t>2026-09-06_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2917,60 +2953,60 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>鴻海精密工業</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>鴻海精密工業</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>3.39%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>629000</v>
+        <v>736000</v>
       </c>
       <c r="K41" t="n">
-        <v>1021000</v>
+        <v>686000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>392,000</t>
+          <t>-50,000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-09-06_00985A_full_holdings.xlsx</t>
+          <t>2026-09-06_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2985,55 +3021,55 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>金像電子（股）公司</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>金像電子（股）公司</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>2.35%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>19000</v>
+        <v>650000</v>
       </c>
       <c r="K42" t="n">
-        <v>1000</v>
+        <v>580000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-18,000</t>
+          <t>-70,000</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-09-06_00985A_full_holdings.xlsx</t>
+          <t>2026-09-06_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3043,60 +3079,60 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>313000</v>
+        <v>4500000</v>
       </c>
       <c r="K43" t="n">
-        <v>444000</v>
+        <v>4000000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>131,000</t>
+          <t>-500,000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-09-06_00985A_full_holdings.xlsx</t>
+          <t>2026-09-06_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3111,48 +3147,48 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>27000</v>
+        <v>1737000</v>
       </c>
       <c r="K44" t="n">
-        <v>1000</v>
+        <v>1580000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-26,000</t>
+          <t>-157,000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-06_00985A_full_holdings.xlsx</t>
+          <t>2026-09-06_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -3164,55 +3200,37 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3105</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>穩懋半導體</t>
-        </is>
-      </c>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>穩懋半導體</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>0.87%</t>
-        </is>
-      </c>
+          <t>微星科技</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>-0.86%</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>203000</v>
-      </c>
+          <t>1.86%</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>-201,000</t>
-        </is>
-      </c>
+        <v>1213000</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>2026-09-06_00985A_full_holdings.xlsx</t>
@@ -3227,55 +3245,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>景碩科技</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>景碩科技</t>
-        </is>
-      </c>
+          <t>臻鼎科技控股</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>-1,000</t>
-        </is>
-      </c>
+        <v>46000</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>2026-09-06_00985A_full_holdings.xlsx</t>
@@ -3300,43 +3300,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>緯穎科技服務</t>
+          <t>大成不銹鋼工業</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>緯穎科技服務</t>
+          <t>大成不銹鋼工業</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>167036</v>
+        <v>4181000</v>
       </c>
       <c r="K47" t="n">
-        <v>114036</v>
+        <v>2097000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-53,000</t>
+          <t>-2,084,000</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3358,48 +3358,48 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>群聯電子</t>
+          <t>鴻海精密工業</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>群聯電子</t>
+          <t>鴻海精密工業</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>2.48%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.98%</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>9000</v>
+        <v>629000</v>
       </c>
       <c r="K48" t="n">
-        <v>1000</v>
+        <v>1021000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-8,000</t>
+          <t>392,000</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3411,7 +3411,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3421,60 +3421,60 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>金像電子（股）公司</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>金像電子（股）公司</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>123000</v>
+        <v>19000</v>
       </c>
       <c r="K49" t="n">
-        <v>175000</v>
+        <v>1000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>52,000</t>
+          <t>-18,000</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-06_00400A_full_holdings.xlsx</t>
+          <t>2026-09-06_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3484,60 +3484,60 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>154000</v>
+        <v>313000</v>
       </c>
       <c r="K50" t="n">
-        <v>121000</v>
+        <v>444000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-33,000</t>
+          <t>131,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-06_00400A_full_holdings.xlsx</t>
+          <t>2026-09-06_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3547,114 +3547,555 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>文曄科技</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>文曄科技</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>4.13%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4.42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>336000</v>
+        <v>27000</v>
       </c>
       <c r="K51" t="n">
-        <v>377000</v>
+        <v>1000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>41,000</t>
+          <t>-26,000</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-09-06_00400A_full_holdings.xlsx</t>
+          <t>2026-09-06_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>穩懋半導體</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>穩懋半導體</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>-0.86%</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>203000</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>-201,000</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09-06_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>-1,000</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09-06_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>緯穎科技服務</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>緯穎科技服務</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3.99%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2.78%</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>-1.21%</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>167036</v>
+      </c>
+      <c r="K54" t="n">
+        <v>114036</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>-53,000</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09-06_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>-0.15%</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>9000</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09-06_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>00400A</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2.29%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>3.30%</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>+1.01%</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>123000</v>
+      </c>
+      <c r="K56" t="n">
+        <v>175000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>52,000</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09-06_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>3.92%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2.77%</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>-1.15%</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>154000</v>
+      </c>
+      <c r="K57" t="n">
+        <v>121000</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>-33,000</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-09-06_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>4.13%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>4.42%</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>+0.29%</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>336000</v>
+      </c>
+      <c r="K58" t="n">
+        <v>377000</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>41,000</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09-06_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>3037</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>欣興</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>欣興</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>2.81%</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>3.94%</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>+1.13%</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="J59" t="n">
         <v>907000</v>
       </c>
-      <c r="K52" t="n">
+      <c r="K59" t="n">
         <v>1209000</v>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>302,000</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>2026-09-06_00400A_full_holdings.xlsx</t>
         </is>
